--- a/data-exports/cyber_incident_sample_data.xlsx
+++ b/data-exports/cyber_incident_sample_data.xlsx
@@ -2,128 +2,41 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2080" yWindow="60" windowWidth="25600" windowHeight="19820" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Directions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Page 1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choice_values" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sample Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="choice_values1">choice_values!$B$1:$B$6</definedName>
-    <definedName name="choice_values3">choice_values!$D$1:$D$4</definedName>
-    <definedName name="choice_values7">choice_values!$H$1:$H$19</definedName>
-    <definedName name="choice_values11">choice_values!$L$1:$L$6</definedName>
-    <definedName name="choice_values18">choice_values!$S$1:$S$6</definedName>
-    <definedName name="choice_values28">choice_values!$AC$1:$AC$4</definedName>
-    <definedName name="choice_values31">choice_values!$AF$1:$AF$4</definedName>
-    <definedName name="choice_values38">choice_values!$AM$1:$AM$5</definedName>
-    <definedName name="choice_values45">choice_values!$AT$1:$AT$5</definedName>
-    <definedName name="choice_values51">choice_values!$AZ$1:$AZ$6</definedName>
-    <definedName name="choice_values52">choice_values!$BA$1:$BA$10</definedName>
-    <definedName name="choice_values54">choice_values!$BC$1:$BC$3</definedName>
-    <definedName name="choice_values55">choice_values!$BD$1:$BD$3</definedName>
-    <definedName name="choice_values56">choice_values!$BE$1:$BE$3</definedName>
-  </definedNames>
-  <calcPr calcId="140000" fullCalcOnLoad="1" concurrentCalc="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="yyyy-MM-dd HH:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy-MM-dd"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd hh:mm:ss"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="12"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color indexed="63"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color indexed="63"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="FF505050"/>
-      <sz val="20"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color theme="1"/>
-      <sz val="14"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="26"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="FF505050"/>
-      <sz val="26"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="FF505050"/>
-      <sz val="14"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="FFFF0000"/>
-      <sz val="12"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="FFFF0000"/>
-      <sz val="14"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF636363"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -138,61 +51,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -262,98 +130,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>292100</colOff>
-      <row>78</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>7</col>
-      <colOff>546100</colOff>
-      <row>100</row>
-      <rowOff>165100</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1068" name="Picture 6"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1384300" y="14859000"/>
-          <a:ext cx="4381500" cy="4356100"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>4302</colOff>
-      <row>12</row>
-      <rowOff>165100</rowOff>
-    </from>
-    <to>
-      <col>20</col>
-      <colOff>452898</colOff>
-      <row>67</row>
-      <rowOff>63500</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1069" name="Picture 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="4302" y="2400300"/>
-          <a:ext cx="16941663" cy="10143067"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -431,7 +207,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -466,7 +241,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -501,16 +275,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -632,46 +410,7 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -682,524 +421,328 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:XFD87"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.5" customWidth="1" style="4" min="1" max="1"/>
-    <col width="10.83203125" customWidth="1" style="4" min="3" max="3"/>
-    <col width="16.83203125" customWidth="1" style="4" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customFormat="1" customHeight="1" s="10">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>Importing New Data</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customFormat="1" customHeight="1" s="10"/>
-    <row r="3" ht="15" customFormat="1" customHeight="1" s="10"/>
-    <row r="5" ht="15" customHeight="1" s="4">
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Quick Start Guide</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="n"/>
-      <c r="F5" s="1" t="n"/>
-      <c r="G5" s="1" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="4">
-      <c r="E6" s="1" t="n"/>
-      <c r="F6" s="1" t="n"/>
-      <c r="G6" s="1" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="4">
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>This is a guide to demonstrate the basics of adding new records to a table.</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="4">
-      <c r="K8" s="2" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="4">
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Note:  If you want to update existing records, use the Update Template instead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="70">
-      <c r="B70" s="11" t="inlineStr">
-        <is>
-          <t>Adding Records</t>
-        </is>
-      </c>
-    </row>
-    <row r="71"/>
-    <row r="73" ht="15" customHeight="1" s="4">
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>Add a row for each record you want to add to the table.</t>
-        </is>
-      </c>
-      <c r="K73" s="3" t="n"/>
-      <c r="L73" s="3" t="n"/>
-      <c r="M73" s="3" t="n"/>
-      <c r="N73" s="3" t="n"/>
-      <c r="O73" s="3" t="n"/>
-      <c r="P73" s="3" t="n"/>
-      <c r="Q73" s="3" t="n"/>
-      <c r="R73" s="3" t="n"/>
-      <c r="S73" s="3" t="n"/>
-      <c r="T73" s="3" t="n"/>
-    </row>
-    <row r="74" ht="15" customHeight="1" s="4">
-      <c r="K74" s="3" t="n"/>
-      <c r="L74" s="3" t="n"/>
-      <c r="M74" s="3" t="n"/>
-      <c r="N74" s="3" t="n"/>
-      <c r="O74" s="3" t="n"/>
-      <c r="P74" s="3" t="n"/>
-      <c r="Q74" s="3" t="n"/>
-      <c r="R74" s="3" t="n"/>
-      <c r="S74" s="3" t="n"/>
-      <c r="T74" s="3" t="n"/>
-    </row>
-    <row r="75" ht="15" customHeight="1" s="4">
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>You do not have to add data for every column.</t>
-        </is>
-      </c>
-      <c r="L75" s="3" t="n"/>
-      <c r="M75" s="3" t="n"/>
-      <c r="N75" s="3" t="n"/>
-      <c r="O75" s="3" t="n"/>
-      <c r="P75" s="3" t="n"/>
-      <c r="Q75" s="3" t="n"/>
-      <c r="R75" s="3" t="n"/>
-      <c r="S75" s="3" t="n"/>
-      <c r="T75" s="3" t="n"/>
-    </row>
-    <row r="76" ht="15" customHeight="1" s="4"/>
-    <row r="77">
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>If you want to paste data from another spreadsheet, use the Paste Special command and paste values only to match the existing formatting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80" ht="15" customHeight="1" s="4">
-      <c r="B80" s="7" t="n"/>
-    </row>
-    <row r="81" ht="15" customHeight="1" s="4"/>
-    <row r="82"/>
-    <row r="83" ht="15" customHeight="1" s="4">
-      <c r="B83" s="8" t="n"/>
-    </row>
-    <row r="84" ht="15" customHeight="1" s="4"/>
-    <row r="85">
-      <c r="B85" s="5" t="n"/>
-    </row>
-    <row r="86"/>
-    <row r="87"/>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B80:F81"/>
-    <mergeCell ref="B77:M78"/>
-    <mergeCell ref="B7:J8"/>
-    <mergeCell ref="A1:XFD3"/>
-    <mergeCell ref="B5:D6"/>
-    <mergeCell ref="B73:J74"/>
-    <mergeCell ref="B75:K76"/>
-    <mergeCell ref="B9:J10"/>
-    <mergeCell ref="B85:L85"/>
-    <mergeCell ref="B70:D71"/>
-    <mergeCell ref="B83:M84"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:BH78"/>
+  <dimension ref="A1:BL78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" style="4" min="1" max="1"/>
-    <col width="22" customWidth="1" style="16" min="2" max="2"/>
-    <col width="10" customWidth="1" style="4" min="3" max="3"/>
-    <col width="10" customWidth="1" style="16" min="4" max="4"/>
-    <col width="18" customWidth="1" style="4" min="5" max="5"/>
-    <col width="11" customWidth="1" style="16" min="6" max="6"/>
-    <col width="16" customWidth="1" style="16" min="7" max="7"/>
-    <col width="13" customWidth="1" style="16" min="8" max="8"/>
-    <col width="15" customWidth="1" style="16" min="9" max="9"/>
-    <col width="10" customWidth="1" style="16" min="10" max="10"/>
-    <col width="10" customWidth="1" style="16" min="11" max="11"/>
-    <col width="15" customWidth="1" style="16" min="12" max="12"/>
-    <col width="16" customWidth="1" style="16" min="13" max="13"/>
-    <col width="18" customWidth="1" style="4" min="14" max="14"/>
-    <col width="10" customWidth="1" style="16" min="15" max="15"/>
-    <col width="18" customWidth="1" style="16" min="16" max="16"/>
-    <col width="23" customWidth="1" style="16" min="17" max="17"/>
-    <col width="10" customWidth="1" style="16" min="18" max="18"/>
-    <col width="12" customWidth="1" style="16" min="19" max="19"/>
-    <col width="17" customWidth="1" style="16" min="20" max="20"/>
-    <col width="10" customWidth="1" style="16" min="21" max="21"/>
-    <col width="19" customWidth="1" style="16" min="22" max="22"/>
-    <col width="14" customWidth="1" style="16" min="23" max="23"/>
-    <col width="18" customWidth="1" style="4" min="24" max="24"/>
-    <col width="13" customWidth="1" style="16" min="25" max="25"/>
-    <col width="13" customWidth="1" style="16" min="26" max="26"/>
-    <col width="11" customWidth="1" style="16" min="27" max="27"/>
-    <col width="18" customWidth="1" style="4" min="28" max="28"/>
-    <col width="34" customWidth="1" style="16" min="29" max="29"/>
-    <col width="18" customWidth="1" style="4" min="30" max="30"/>
-    <col width="18" customWidth="1" style="4" min="31" max="31"/>
-    <col width="10" customWidth="1" style="4" min="32" max="32"/>
-    <col width="10" customWidth="1" style="4" min="33" max="33"/>
-    <col width="10" customWidth="1" style="16" min="34" max="34"/>
-    <col width="10" customWidth="1" style="4" min="35" max="35"/>
-    <col width="19" customWidth="1" style="16" min="36" max="36"/>
-    <col width="28" customWidth="1" style="4" min="37" max="37"/>
-    <col width="10" customWidth="1" style="16" min="38" max="38"/>
-    <col width="14" customWidth="1" style="16" min="39" max="39"/>
-    <col width="18" customWidth="1" style="4" min="40" max="40"/>
-    <col width="10" customWidth="1" style="16" min="41" max="41"/>
-    <col width="10" customWidth="1" style="4" min="42" max="42"/>
-    <col width="10" customWidth="1" style="16" min="43" max="43"/>
-    <col width="18" customWidth="1" style="4" min="44" max="44"/>
-    <col width="17" customWidth="1" style="4" min="45" max="45"/>
-    <col width="10" customWidth="1" style="4" min="46" max="46"/>
-    <col width="34" customWidth="1" style="4" min="47" max="47"/>
-    <col width="31" customWidth="1" style="4" min="48" max="48"/>
-    <col width="18" customWidth="1" style="4" min="49" max="49"/>
-    <col width="16" customWidth="1" style="16" min="50" max="50"/>
-    <col width="17" customWidth="1" style="16" min="51" max="51"/>
-    <col width="27" customWidth="1" style="16" min="52" max="52"/>
-    <col width="15" customWidth="1" style="16" min="53" max="53"/>
-    <col width="17" customWidth="1" style="16" min="54" max="54"/>
-    <col width="13" customWidth="1" style="16" min="55" max="55"/>
-    <col width="11" customWidth="1" style="16" min="56" max="56"/>
-    <col width="10" customWidth="1" style="4" min="57" max="57"/>
-    <col width="18" customWidth="1" style="4" min="58" max="58"/>
-    <col width="18" customWidth="1" style="4" min="59" max="59"/>
-    <col width="18" customWidth="1" style="4" min="60" max="60"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Acknowledged time</t>
         </is>
       </c>
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ACSC incident severity</t>
         </is>
       </c>
-      <c r="C1" s="17" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="D1" s="17" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Approval</t>
         </is>
       </c>
-      <c r="E1" s="17" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Approval set</t>
         </is>
       </c>
-      <c r="F1" s="17" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Assigned to</t>
         </is>
       </c>
-      <c r="G1" s="17" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Assignment group</t>
         </is>
       </c>
-      <c r="H1" s="17" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Attack vector</t>
         </is>
       </c>
-      <c r="I1" s="17" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Awareness Basis</t>
         </is>
       </c>
-      <c r="J1" s="17" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="K1" s="17" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Caller</t>
         </is>
       </c>
-      <c r="L1" s="17" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Resolution code</t>
         </is>
       </c>
-      <c r="M1" s="17" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Resolution notes</t>
         </is>
       </c>
-      <c r="N1" s="17" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="O1" s="17" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Closed by</t>
         </is>
       </c>
-      <c r="P1" s="17" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Configuration item</t>
         </is>
       </c>
-      <c r="Q1" s="17" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Comments and work notes</t>
         </is>
       </c>
-      <c r="R1" s="17" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="S1" s="17" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Contact type</t>
         </is>
       </c>
-      <c r="T1" s="17" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Containment notes</t>
         </is>
       </c>
-      <c r="U1" s="17" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="V1" s="17" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Correlation display</t>
         </is>
       </c>
-      <c r="W1" s="17" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Correlation ID</t>
         </is>
       </c>
-      <c r="X1" s="17" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Date / time became aware</t>
         </is>
       </c>
-      <c r="Y1" s="17" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Delivery plan</t>
         </is>
       </c>
-      <c r="Z1" s="17" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Delivery task</t>
         </is>
       </c>
-      <c r="AA1" s="17" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="AB1" s="17" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Due date</t>
         </is>
       </c>
-      <c r="AC1" s="17" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Eligible data breach determination</t>
         </is>
       </c>
-      <c r="AD1" s="17" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Expected start</t>
         </is>
       </c>
-      <c r="AE1" s="17" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Follow up</t>
         </is>
       </c>
-      <c r="AF1" s="17" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="AG1" s="17" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Knowledge</t>
         </is>
       </c>
-      <c r="AH1" s="17" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="AI1" s="17" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Made SLA</t>
         </is>
       </c>
-      <c r="AJ1" s="17" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>MITRE ATT&amp;CK tactic</t>
         </is>
       </c>
-      <c r="AK1" s="17" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Notification required to ASD</t>
         </is>
       </c>
-      <c r="AL1" s="17" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Number</t>
         </is>
       </c>
-      <c r="AM1" s="17" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>On hold reason</t>
         </is>
       </c>
-      <c r="AN1" s="17" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Opened</t>
         </is>
       </c>
-      <c r="AO1" s="17" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Opened by</t>
         </is>
       </c>
-      <c r="AP1" s="17" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="AQ1" s="17" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
-      <c r="AR1" s="17" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Ransomware payment date / time</t>
         </is>
       </c>
-      <c r="AS1" s="17" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Persistent threat</t>
         </is>
       </c>
-      <c r="AT1" s="17" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="AU1" s="17" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Ransom / extortion demand resolved</t>
         </is>
       </c>
-      <c r="AV1" s="17" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Ransom / extortion payment made</t>
         </is>
       </c>
-      <c r="AW1" s="17" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Reassignment count</t>
         </is>
       </c>
-      <c r="AX1" s="17" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Service offering</t>
         </is>
       </c>
-      <c r="AY1" s="17" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>Short description</t>
         </is>
       </c>
-      <c r="AZ1" s="17" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>Threat actor classification</t>
         </is>
       </c>
-      <c r="BA1" s="17" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>Threat category</t>
         </is>
       </c>
-      <c r="BB1" s="17" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>Universal Request</t>
         </is>
       </c>
-      <c r="BC1" s="17" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>Upon approval</t>
         </is>
       </c>
-      <c r="BD1" s="17" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>Upon reject</t>
         </is>
       </c>
-      <c r="BE1" s="17" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>Urgency</t>
         </is>
       </c>
-      <c r="BF1" s="17" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Actual end</t>
         </is>
       </c>
-      <c r="BG1" s="17" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Actual start</t>
         </is>
       </c>
-      <c r="BH1" s="17" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>State</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>Data classification of affected assets</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>Affected asset type</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>ACSC Essential Eight control gap</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>Containment method</t>
         </is>
       </c>
     </row>
@@ -1242,7 +785,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N2" s="18" t="n">
+      <c r="N2" s="3" t="n">
         <v>45970.2925462963</v>
       </c>
       <c r="O2" t="inlineStr">
@@ -1265,7 +808,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X2" s="18" t="n">
+      <c r="X2" s="3" t="n">
         <v>45964.5847337963</v>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1278,7 +821,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN2" s="18" t="n">
+      <c r="AN2" s="3" t="n">
         <v>45964.60973379629</v>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1314,6 +857,26 @@
       <c r="BH2" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>configure_macros</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1356,7 +919,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N3" s="18" t="n">
+      <c r="N3" s="3" t="n">
         <v>45977.19270833334</v>
       </c>
       <c r="O3" t="inlineStr">
@@ -1379,7 +942,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X3" s="18" t="n">
+      <c r="X3" s="3" t="n">
         <v>45966.69707175926</v>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1392,7 +955,7 @@
           <t>I1 — Full outage</t>
         </is>
       </c>
-      <c r="AN3" s="18" t="n">
+      <c r="AN3" s="3" t="n">
         <v>45966.70957175926</v>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1428,6 +991,26 @@
       <c r="BH3" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>sensitive_operational</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>regulated_essential_services</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>backups</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>network_isolation</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1053,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N4" s="18" t="n">
+      <c r="N4" s="3" t="n">
         <v>45974.35409722223</v>
       </c>
       <c r="O4" t="inlineStr">
@@ -1493,7 +1076,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X4" s="18" t="n">
+      <c r="X4" s="3" t="n">
         <v>45969.5427662037</v>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1506,7 +1089,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN4" s="18" t="n">
+      <c r="AN4" s="3" t="n">
         <v>45969.55734953703</v>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1542,6 +1125,26 @@
       <c r="BH4" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>configure_macros</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1187,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N5" s="18" t="n">
+      <c r="N5" s="3" t="n">
         <v>45988.42038194444</v>
       </c>
       <c r="O5" t="inlineStr">
@@ -1607,7 +1210,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X5" s="18" t="n">
+      <c r="X5" s="3" t="n">
         <v>45982.32450231481</v>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1620,7 +1223,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN5" s="18" t="n">
+      <c r="AN5" s="3" t="n">
         <v>45982.33144675926</v>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1656,6 +1259,26 @@
       <c r="BH5" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1321,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N6" s="18" t="n">
+      <c r="N6" s="3" t="n">
         <v>45987.97355324074</v>
       </c>
       <c r="O6" t="inlineStr">
@@ -1721,7 +1344,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X6" s="18" t="n">
+      <c r="X6" s="3" t="n">
         <v>45982.68488425926</v>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1734,7 +1357,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN6" s="18" t="n">
+      <c r="AN6" s="3" t="n">
         <v>45982.72446759259</v>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1770,6 +1393,26 @@
       <c r="BH6" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>sensitive_operational</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>account_disable</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1455,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N7" s="18" t="n">
+      <c r="N7" s="3" t="n">
         <v>46005.58629629629</v>
       </c>
       <c r="O7" t="inlineStr">
@@ -1835,7 +1478,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X7" s="18" t="n">
+      <c r="X7" s="3" t="n">
         <v>46000.70888888889</v>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1853,7 +1496,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN7" s="18" t="n">
+      <c r="AN7" s="3" t="n">
         <v>46000.74777777777</v>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1889,6 +1532,26 @@
       <c r="BH7" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>private_information</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>undetermined</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1594,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N8" s="18" t="n">
+      <c r="N8" s="3" t="n">
         <v>46018.4186574074</v>
       </c>
       <c r="O8" t="inlineStr">
@@ -1954,7 +1617,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X8" s="18" t="n">
+      <c r="X8" s="3" t="n">
         <v>46014.47024305556</v>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1967,7 +1630,7 @@
           <t>I2 — Widespread degradation</t>
         </is>
       </c>
-      <c r="AN8" s="18" t="n">
+      <c r="AN8" s="3" t="n">
         <v>46014.50149305556</v>
       </c>
       <c r="AO8" t="inlineStr">
@@ -2003,6 +1666,26 @@
       <c r="BH8" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>configure_macros</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -2045,7 +1728,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N9" s="18" t="n">
+      <c r="N9" s="3" t="n">
         <v>46024.15247685185</v>
       </c>
       <c r="O9" t="inlineStr">
@@ -2068,7 +1751,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X9" s="18" t="n">
+      <c r="X9" s="3" t="n">
         <v>46016.42041666667</v>
       </c>
       <c r="AA9" t="inlineStr">
@@ -2081,7 +1764,7 @@
           <t>I2 — Widespread degradation</t>
         </is>
       </c>
-      <c r="AN9" s="18" t="n">
+      <c r="AN9" s="3" t="n">
         <v>46016.45166666667</v>
       </c>
       <c r="AO9" t="inlineStr">
@@ -2117,6 +1800,26 @@
       <c r="BH9" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -2159,7 +1862,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N10" s="18" t="n">
+      <c r="N10" s="3" t="n">
         <v>46024.57790509259</v>
       </c>
       <c r="O10" t="inlineStr">
@@ -2182,7 +1885,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X10" s="18" t="n">
+      <c r="X10" s="3" t="n">
         <v>46019.42836805555</v>
       </c>
       <c r="AA10" t="inlineStr">
@@ -2195,7 +1898,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN10" s="18" t="n">
+      <c r="AN10" s="3" t="n">
         <v>46019.45822916667</v>
       </c>
       <c r="AO10" t="inlineStr">
@@ -2231,6 +1934,26 @@
       <c r="BH10" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>configure_macros</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -2273,7 +1996,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N11" s="18" t="n">
+      <c r="N11" s="3" t="n">
         <v>46032.86134259259</v>
       </c>
       <c r="O11" t="inlineStr">
@@ -2296,7 +2019,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X11" s="18" t="n">
+      <c r="X11" s="3" t="n">
         <v>46026.47893518519</v>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2314,7 +2037,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN11" s="18" t="n">
+      <c r="AN11" s="3" t="n">
         <v>46026.50740740741</v>
       </c>
       <c r="AO11" t="inlineStr">
@@ -2350,6 +2073,26 @@
       <c r="BH11" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>private_information</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>harden_apps</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2135,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N12" s="18" t="n">
+      <c r="N12" s="3" t="n">
         <v>46032.14881944445</v>
       </c>
       <c r="O12" t="inlineStr">
@@ -2415,7 +2158,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X12" s="18" t="n">
+      <c r="X12" s="3" t="n">
         <v>46028.46784722222</v>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2428,7 +2171,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN12" s="18" t="n">
+      <c r="AN12" s="3" t="n">
         <v>46028.526875</v>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2464,6 +2207,26 @@
       <c r="BH12" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>configure_macros</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2269,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N13" s="18" t="n">
+      <c r="N13" s="3" t="n">
         <v>46041.78363425926</v>
       </c>
       <c r="O13" t="inlineStr">
@@ -2529,7 +2292,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X13" s="18" t="n">
+      <c r="X13" s="3" t="n">
         <v>46032.77773148148</v>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2542,7 +2305,7 @@
           <t>I2 — Widespread degradation</t>
         </is>
       </c>
-      <c r="AN13" s="18" t="n">
+      <c r="AN13" s="3" t="n">
         <v>46032.79162037037</v>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2578,6 +2341,26 @@
       <c r="BH13" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>regulated_essential_services</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>undetermined</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>firewall_rule</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2403,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N14" s="18" t="n">
+      <c r="N14" s="3" t="n">
         <v>46041.69175925926</v>
       </c>
       <c r="O14" t="inlineStr">
@@ -2643,7 +2426,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X14" s="18" t="n">
+      <c r="X14" s="3" t="n">
         <v>46037.58291666667</v>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2656,7 +2439,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN14" s="18" t="n">
+      <c r="AN14" s="3" t="n">
         <v>46037.60791666667</v>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2692,6 +2475,26 @@
       <c r="BH14" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>configure_macros</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2537,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N15" s="18" t="n">
+      <c r="N15" s="3" t="n">
         <v>46045.19355324074</v>
       </c>
       <c r="O15" t="inlineStr">
@@ -2757,7 +2560,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X15" s="18" t="n">
+      <c r="X15" s="3" t="n">
         <v>46041.33613425926</v>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2770,7 +2573,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN15" s="18" t="n">
+      <c r="AN15" s="3" t="n">
         <v>46041.35835648148</v>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2806,6 +2609,26 @@
       <c r="BH15" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>sensitive_operational</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>account_disable</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2671,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N16" s="18" t="n">
+      <c r="N16" s="3" t="n">
         <v>46053.15924768519</v>
       </c>
       <c r="O16" t="inlineStr">
@@ -2871,7 +2694,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X16" s="18" t="n">
+      <c r="X16" s="3" t="n">
         <v>46047.37909722222</v>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2884,7 +2707,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN16" s="18" t="n">
+      <c r="AN16" s="3" t="n">
         <v>46047.419375</v>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2920,6 +2743,26 @@
       <c r="BH16" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>configure_macros</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2805,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N17" s="18" t="n">
+      <c r="N17" s="3" t="n">
         <v>46077.34916666667</v>
       </c>
       <c r="O17" t="inlineStr">
@@ -2985,7 +2828,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X17" s="18" t="n">
+      <c r="X17" s="3" t="n">
         <v>46064.46126157408</v>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2998,7 +2841,7 @@
           <t>I1 — Full outage</t>
         </is>
       </c>
-      <c r="AN17" s="18" t="n">
+      <c r="AN17" s="3" t="n">
         <v>46064.47584490741</v>
       </c>
       <c r="AO17" t="inlineStr">
@@ -3034,6 +2877,26 @@
       <c r="BH17" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>sensitive_operational</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>regulated_essential_services</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>backups</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>network_isolation</t>
         </is>
       </c>
     </row>
@@ -3076,7 +2939,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N18" s="18" t="n">
+      <c r="N18" s="3" t="n">
         <v>46080.26141203703</v>
       </c>
       <c r="O18" t="inlineStr">
@@ -3099,7 +2962,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X18" s="18" t="n">
+      <c r="X18" s="3" t="n">
         <v>46074.67688657407</v>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3112,7 +2975,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN18" s="18" t="n">
+      <c r="AN18" s="3" t="n">
         <v>46074.71369212963</v>
       </c>
       <c r="AO18" t="inlineStr">
@@ -3148,6 +3011,26 @@
       <c r="BH18" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>sensitive_operational</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>account_disable</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3073,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N19" s="18" t="n">
+      <c r="N19" s="3" t="n">
         <v>46082.27842592593</v>
       </c>
       <c r="O19" t="inlineStr">
@@ -3213,7 +3096,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X19" s="18" t="n">
+      <c r="X19" s="3" t="n">
         <v>46075.65185185185</v>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3226,7 +3109,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN19" s="18" t="n">
+      <c r="AN19" s="3" t="n">
         <v>46075.66643518519</v>
       </c>
       <c r="AO19" t="inlineStr">
@@ -3262,6 +3145,26 @@
       <c r="BH19" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3207,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N20" s="18" t="n">
+      <c r="N20" s="3" t="n">
         <v>46082.54193287037</v>
       </c>
       <c r="O20" t="inlineStr">
@@ -3327,7 +3230,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X20" s="18" t="n">
+      <c r="X20" s="3" t="n">
         <v>46077.39541666667</v>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3340,7 +3243,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN20" s="18" t="n">
+      <c r="AN20" s="3" t="n">
         <v>46077.43222222223</v>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3376,6 +3279,26 @@
       <c r="BH20" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3341,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N21" s="18" t="n">
+      <c r="N21" s="3" t="n">
         <v>46083.4455787037</v>
       </c>
       <c r="O21" t="inlineStr">
@@ -3441,7 +3364,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X21" s="18" t="n">
+      <c r="X21" s="3" t="n">
         <v>46078.71865740741</v>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3454,7 +3377,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN21" s="18" t="n">
+      <c r="AN21" s="3" t="n">
         <v>46078.76657407408</v>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3490,6 +3413,26 @@
       <c r="BH21" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3475,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N22" s="18" t="n">
+      <c r="N22" s="3" t="n">
         <v>46101.18925925926</v>
       </c>
       <c r="O22" t="inlineStr">
@@ -3555,7 +3498,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X22" s="18" t="n">
+      <c r="X22" s="3" t="n">
         <v>46094.47885416666</v>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3568,7 +3511,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN22" s="18" t="n">
+      <c r="AN22" s="3" t="n">
         <v>46094.52329861111</v>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3604,6 +3547,26 @@
       <c r="BH22" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>configure_macros</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3609,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N23" s="18" t="n">
+      <c r="N23" s="3" t="n">
         <v>46100.17568287037</v>
       </c>
       <c r="O23" t="inlineStr">
@@ -3669,7 +3632,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X23" s="18" t="n">
+      <c r="X23" s="3" t="n">
         <v>46097.21105324074</v>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3682,7 +3645,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN23" s="18" t="n">
+      <c r="AN23" s="3" t="n">
         <v>46097.23744212963</v>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3718,6 +3681,26 @@
       <c r="BH23" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>configure_macros</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3743,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N24" s="18" t="n">
+      <c r="N24" s="3" t="n">
         <v>46104.62171296297</v>
       </c>
       <c r="O24" t="inlineStr">
@@ -3783,7 +3766,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X24" s="18" t="n">
+      <c r="X24" s="3" t="n">
         <v>46099.74283564815</v>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3796,7 +3779,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN24" s="18" t="n">
+      <c r="AN24" s="3" t="n">
         <v>46099.75394675926</v>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3832,6 +3815,26 @@
       <c r="BH24" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ24" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK24" t="inlineStr">
+        <is>
+          <t>configure_macros</t>
+        </is>
+      </c>
+      <c r="BL24" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3877,7 @@
           <t>Internal remediation complete. Details referred to police via ReportCyber.</t>
         </is>
       </c>
-      <c r="N25" s="18" t="n">
+      <c r="N25" s="3" t="n">
         <v>46107.09234953704</v>
       </c>
       <c r="O25" t="inlineStr">
@@ -3897,7 +3900,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X25" s="18" t="n">
+      <c r="X25" s="3" t="n">
         <v>46099.79216435185</v>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3910,7 +3913,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN25" s="18" t="n">
+      <c r="AN25" s="3" t="n">
         <v>46099.80605324074</v>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3946,6 +3949,26 @@
       <c r="BH25" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>sensitive_operational</t>
+        </is>
+      </c>
+      <c r="BJ25" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK25" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL25" t="inlineStr">
+        <is>
+          <t>account_disable</t>
         </is>
       </c>
     </row>
@@ -3988,7 +4011,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N26" s="18" t="n">
+      <c r="N26" s="3" t="n">
         <v>46106.66516203704</v>
       </c>
       <c r="O26" t="inlineStr">
@@ -4011,7 +4034,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X26" s="18" t="n">
+      <c r="X26" s="3" t="n">
         <v>46100.84737268519</v>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4024,7 +4047,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN26" s="18" t="n">
+      <c r="AN26" s="3" t="n">
         <v>46100.87515046296</v>
       </c>
       <c r="AO26" t="inlineStr">
@@ -4060,6 +4083,26 @@
       <c r="BH26" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>sensitive_operational</t>
+        </is>
+      </c>
+      <c r="BJ26" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK26" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL26" t="inlineStr">
+        <is>
+          <t>account_disable</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4145,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N27" s="18" t="n">
+      <c r="N27" s="3" t="n">
         <v>46106.18063657408</v>
       </c>
       <c r="O27" t="inlineStr">
@@ -4125,7 +4168,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X27" s="18" t="n">
+      <c r="X27" s="3" t="n">
         <v>46102.32184027778</v>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4138,7 +4181,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN27" s="18" t="n">
+      <c r="AN27" s="3" t="n">
         <v>46102.33503472222</v>
       </c>
       <c r="AO27" t="inlineStr">
@@ -4174,6 +4217,26 @@
       <c r="BH27" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ27" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK27" t="inlineStr">
+        <is>
+          <t>configure_macros</t>
+        </is>
+      </c>
+      <c r="BL27" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4279,7 @@
           <t>Investigation found the activity was legitimate. Detection rule tuned to reduce noise.</t>
         </is>
       </c>
-      <c r="N28" s="18" t="n">
+      <c r="N28" s="3" t="n">
         <v>46112.40692129629</v>
       </c>
       <c r="O28" t="inlineStr">
@@ -4239,7 +4302,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X28" s="18" t="n">
+      <c r="X28" s="3" t="n">
         <v>46105.59498842592</v>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4252,7 +4315,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN28" s="18" t="n">
+      <c r="AN28" s="3" t="n">
         <v>46105.63596064815</v>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4288,6 +4351,26 @@
       <c r="BH28" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ28" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK28" t="inlineStr">
+        <is>
+          <t>configure_macros</t>
+        </is>
+      </c>
+      <c r="BL28" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4413,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N29" s="18" t="n">
+      <c r="N29" s="3" t="n">
         <v>46115.96673611111</v>
       </c>
       <c r="O29" t="inlineStr">
@@ -4353,7 +4436,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X29" s="18" t="n">
+      <c r="X29" s="3" t="n">
         <v>46110.59946759259</v>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4366,7 +4449,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN29" s="18" t="n">
+      <c r="AN29" s="3" t="n">
         <v>46110.6057175926</v>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4402,6 +4485,26 @@
       <c r="BH29" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ29" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK29" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL29" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4547,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N30" s="18" t="n">
+      <c r="N30" s="3" t="n">
         <v>46118.51805555556</v>
       </c>
       <c r="O30" t="inlineStr">
@@ -4467,7 +4570,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X30" s="18" t="n">
+      <c r="X30" s="3" t="n">
         <v>46111.63143518518</v>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4480,7 +4583,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN30" s="18" t="n">
+      <c r="AN30" s="3" t="n">
         <v>46111.64115740741</v>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4516,6 +4619,26 @@
       <c r="BH30" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ30" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK30" t="inlineStr">
+        <is>
+          <t>configure_macros</t>
+        </is>
+      </c>
+      <c r="BL30" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4681,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N31" s="18" t="n">
+      <c r="N31" s="3" t="n">
         <v>46128.91708333333</v>
       </c>
       <c r="O31" t="inlineStr">
@@ -4581,7 +4704,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X31" s="18" t="n">
+      <c r="X31" s="3" t="n">
         <v>46122.52013888889</v>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4594,7 +4717,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN31" s="18" t="n">
+      <c r="AN31" s="3" t="n">
         <v>46122.55208333334</v>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4630,6 +4753,26 @@
       <c r="BH31" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ31" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK31" t="inlineStr">
+        <is>
+          <t>undetermined</t>
+        </is>
+      </c>
+      <c r="BL31" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4815,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N32" s="18" t="n">
+      <c r="N32" s="3" t="n">
         <v>46134.20377314815</v>
       </c>
       <c r="O32" t="inlineStr">
@@ -4695,7 +4838,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X32" s="18" t="n">
+      <c r="X32" s="3" t="n">
         <v>46129.58984953703</v>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4713,7 +4856,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN32" s="18" t="n">
+      <c r="AN32" s="3" t="n">
         <v>46129.64471064815</v>
       </c>
       <c r="AO32" t="inlineStr">
@@ -4749,6 +4892,26 @@
       <c r="BH32" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>private_information</t>
+        </is>
+      </c>
+      <c r="BJ32" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK32" t="inlineStr">
+        <is>
+          <t>harden_apps</t>
+        </is>
+      </c>
+      <c r="BL32" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4954,7 @@
           <t>Vendor released a clean update and confirmed root cause. Agent redeployed after verification.</t>
         </is>
       </c>
-      <c r="N33" s="18" t="n">
+      <c r="N33" s="3" t="n">
         <v>46138.60608796297</v>
       </c>
       <c r="O33" t="inlineStr">
@@ -4814,7 +4977,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X33" s="18" t="n">
+      <c r="X33" s="3" t="n">
         <v>46130.95802083334</v>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4827,7 +4990,7 @@
           <t>I2 — Widespread degradation</t>
         </is>
       </c>
-      <c r="AN33" s="18" t="n">
+      <c r="AN33" s="3" t="n">
         <v>46131.00177083333</v>
       </c>
       <c r="AO33" t="inlineStr">
@@ -4866,6 +5029,26 @@
       <c r="BH33" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ33" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK33" t="inlineStr">
+        <is>
+          <t>undetermined</t>
+        </is>
+      </c>
+      <c r="BL33" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -4908,7 +5091,7 @@
           <t>Vendor released a clean update and confirmed root cause. Agent redeployed after verification.</t>
         </is>
       </c>
-      <c r="N34" s="18" t="n">
+      <c r="N34" s="3" t="n">
         <v>46137.54700231482</v>
       </c>
       <c r="O34" t="inlineStr">
@@ -4931,7 +5114,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X34" s="18" t="n">
+      <c r="X34" s="3" t="n">
         <v>46132.41744212963</v>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4944,7 +5127,7 @@
           <t>I2 — Widespread degradation</t>
         </is>
       </c>
-      <c r="AN34" s="18" t="n">
+      <c r="AN34" s="3" t="n">
         <v>46132.47646990741</v>
       </c>
       <c r="AO34" t="inlineStr">
@@ -4983,6 +5166,26 @@
       <c r="BH34" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ34" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK34" t="inlineStr">
+        <is>
+          <t>undetermined</t>
+        </is>
+      </c>
+      <c r="BL34" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5228,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N35" s="18" t="n">
+      <c r="N35" s="3" t="n">
         <v>46148.593125</v>
       </c>
       <c r="O35" t="inlineStr">
@@ -5048,7 +5251,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X35" s="18" t="n">
+      <c r="X35" s="3" t="n">
         <v>46141.68944444445</v>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5061,7 +5264,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN35" s="18" t="n">
+      <c r="AN35" s="3" t="n">
         <v>46141.71236111111</v>
       </c>
       <c r="AO35" t="inlineStr">
@@ -5097,6 +5300,26 @@
       <c r="BH35" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI35" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ35" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK35" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL35" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -5139,7 +5362,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N36" s="18" t="n">
+      <c r="N36" s="3" t="n">
         <v>46147.50203703704</v>
       </c>
       <c r="O36" t="inlineStr">
@@ -5162,7 +5385,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X36" s="18" t="n">
+      <c r="X36" s="3" t="n">
         <v>46142.27799768518</v>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5175,7 +5398,7 @@
           <t>I2 — Widespread degradation</t>
         </is>
       </c>
-      <c r="AN36" s="18" t="n">
+      <c r="AN36" s="3" t="n">
         <v>46142.33008101852</v>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5211,6 +5434,26 @@
       <c r="BH36" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI36" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ36" t="inlineStr">
+        <is>
+          <t>regulated_essential_services</t>
+        </is>
+      </c>
+      <c r="BK36" t="inlineStr">
+        <is>
+          <t>undetermined</t>
+        </is>
+      </c>
+      <c r="BL36" t="inlineStr">
+        <is>
+          <t>firewall_rule</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5496,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N37" s="18" t="n">
+      <c r="N37" s="3" t="n">
         <v>46152.42625</v>
       </c>
       <c r="O37" t="inlineStr">
@@ -5276,7 +5519,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X37" s="18" t="n">
+      <c r="X37" s="3" t="n">
         <v>46147.64942129629</v>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5289,7 +5532,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN37" s="18" t="n">
+      <c r="AN37" s="3" t="n">
         <v>46147.71122685185</v>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5325,6 +5568,26 @@
       <c r="BH37" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ37" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK37" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL37" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5630,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N38" s="18" t="n">
+      <c r="N38" s="3" t="n">
         <v>46157.10435185185</v>
       </c>
       <c r="O38" t="inlineStr">
@@ -5390,7 +5653,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X38" s="18" t="n">
+      <c r="X38" s="3" t="n">
         <v>46150.83686342592</v>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5403,7 +5666,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN38" s="18" t="n">
+      <c r="AN38" s="3" t="n">
         <v>46150.88200231481</v>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5439,6 +5702,26 @@
       <c r="BH38" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI38" t="inlineStr">
+        <is>
+          <t>sensitive_operational</t>
+        </is>
+      </c>
+      <c r="BJ38" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK38" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL38" t="inlineStr">
+        <is>
+          <t>account_disable</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5764,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N39" s="18" t="n">
+      <c r="N39" s="3" t="n">
         <v>46173.25261574074</v>
       </c>
       <c r="O39" t="inlineStr">
@@ -5504,7 +5787,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X39" s="18" t="n">
+      <c r="X39" s="3" t="n">
         <v>46169.20039351852</v>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5522,7 +5805,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN39" s="18" t="n">
+      <c r="AN39" s="3" t="n">
         <v>46169.20456018519</v>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5558,6 +5841,26 @@
       <c r="BH39" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI39" t="inlineStr">
+        <is>
+          <t>private_information</t>
+        </is>
+      </c>
+      <c r="BJ39" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK39" t="inlineStr">
+        <is>
+          <t>undetermined</t>
+        </is>
+      </c>
+      <c r="BL39" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -5600,7 +5903,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N40" s="18" t="n">
+      <c r="N40" s="3" t="n">
         <v>46177.09090277777</v>
       </c>
       <c r="O40" t="inlineStr">
@@ -5623,7 +5926,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X40" s="18" t="n">
+      <c r="X40" s="3" t="n">
         <v>46170.59304398148</v>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5636,7 +5939,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN40" s="18" t="n">
+      <c r="AN40" s="3" t="n">
         <v>46170.63957175926</v>
       </c>
       <c r="AO40" t="inlineStr">
@@ -5672,6 +5975,26 @@
       <c r="BH40" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ40" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK40" t="inlineStr">
+        <is>
+          <t>app_patching</t>
+        </is>
+      </c>
+      <c r="BL40" t="inlineStr">
+        <is>
+          <t>network_isolation</t>
         </is>
       </c>
     </row>
@@ -5714,7 +6037,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N41" s="18" t="n">
+      <c r="N41" s="3" t="n">
         <v>46177.16864583334</v>
       </c>
       <c r="O41" t="inlineStr">
@@ -5737,7 +6060,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X41" s="18" t="n">
+      <c r="X41" s="3" t="n">
         <v>46171.99396990741</v>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5750,7 +6073,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN41" s="18" t="n">
+      <c r="AN41" s="3" t="n">
         <v>46172.00230324074</v>
       </c>
       <c r="AO41" t="inlineStr">
@@ -5786,6 +6109,26 @@
       <c r="BH41" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ41" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK41" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL41" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -5828,7 +6171,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N42" s="18" t="n">
+      <c r="N42" s="3" t="n">
         <v>46181.70518518519</v>
       </c>
       <c r="O42" t="inlineStr">
@@ -5851,7 +6194,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X42" s="18" t="n">
+      <c r="X42" s="3" t="n">
         <v>46177.37802083333</v>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5864,7 +6207,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN42" s="18" t="n">
+      <c r="AN42" s="3" t="n">
         <v>46177.44052083333</v>
       </c>
       <c r="AO42" t="inlineStr">
@@ -5900,6 +6243,26 @@
       <c r="BH42" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI42" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ42" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK42" t="inlineStr">
+        <is>
+          <t>configure_macros</t>
+        </is>
+      </c>
+      <c r="BL42" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -5942,7 +6305,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N43" s="18" t="n">
+      <c r="N43" s="3" t="n">
         <v>46188.24341435185</v>
       </c>
       <c r="O43" t="inlineStr">
@@ -5965,7 +6328,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X43" s="18" t="n">
+      <c r="X43" s="3" t="n">
         <v>46180.57429398148</v>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5978,7 +6341,7 @@
           <t>I2 — Widespread degradation</t>
         </is>
       </c>
-      <c r="AN43" s="18" t="n">
+      <c r="AN43" s="3" t="n">
         <v>46180.62012731482</v>
       </c>
       <c r="AO43" t="inlineStr">
@@ -6014,6 +6377,26 @@
       <c r="BH43" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI43" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ43" t="inlineStr">
+        <is>
+          <t>regulated_essential_services</t>
+        </is>
+      </c>
+      <c r="BK43" t="inlineStr">
+        <is>
+          <t>undetermined</t>
+        </is>
+      </c>
+      <c r="BL43" t="inlineStr">
+        <is>
+          <t>firewall_rule</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6439,7 @@
           <t>Internal remediation complete. Details referred to police via ReportCyber.</t>
         </is>
       </c>
-      <c r="N44" s="18" t="n">
+      <c r="N44" s="3" t="n">
         <v>46188.44383101852</v>
       </c>
       <c r="O44" t="inlineStr">
@@ -6079,7 +6462,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X44" s="18" t="n">
+      <c r="X44" s="3" t="n">
         <v>46184.17728009259</v>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6092,7 +6475,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN44" s="18" t="n">
+      <c r="AN44" s="3" t="n">
         <v>46184.23561342592</v>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6128,6 +6511,26 @@
       <c r="BH44" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI44" t="inlineStr">
+        <is>
+          <t>sensitive_operational</t>
+        </is>
+      </c>
+      <c r="BJ44" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK44" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL44" t="inlineStr">
+        <is>
+          <t>account_disable</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6573,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N45" s="18" t="n">
+      <c r="N45" s="3" t="n">
         <v>46194.78762731481</v>
       </c>
       <c r="O45" t="inlineStr">
@@ -6193,7 +6596,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X45" s="18" t="n">
+      <c r="X45" s="3" t="n">
         <v>46191.34305555555</v>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6206,7 +6609,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN45" s="18" t="n">
+      <c r="AN45" s="3" t="n">
         <v>46191.39444444444</v>
       </c>
       <c r="AO45" t="inlineStr">
@@ -6242,6 +6645,26 @@
       <c r="BH45" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI45" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ45" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK45" t="inlineStr">
+        <is>
+          <t>configure_macros</t>
+        </is>
+      </c>
+      <c r="BL45" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -6284,7 +6707,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N46" s="18" t="n">
+      <c r="N46" s="3" t="n">
         <v>46199.02603009259</v>
       </c>
       <c r="O46" t="inlineStr">
@@ -6307,7 +6730,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X46" s="18" t="n">
+      <c r="X46" s="3" t="n">
         <v>46194.1284375</v>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6320,7 +6743,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN46" s="18" t="n">
+      <c r="AN46" s="3" t="n">
         <v>46194.18121527778</v>
       </c>
       <c r="AO46" t="inlineStr">
@@ -6356,6 +6779,26 @@
       <c r="BH46" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI46" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ46" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK46" t="inlineStr">
+        <is>
+          <t>configure_macros</t>
+        </is>
+      </c>
+      <c r="BL46" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6841,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N47" s="18" t="n">
+      <c r="N47" s="3" t="n">
         <v>46202.51768518519</v>
       </c>
       <c r="O47" t="inlineStr">
@@ -6421,7 +6864,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X47" s="18" t="n">
+      <c r="X47" s="3" t="n">
         <v>46195.64510416667</v>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6434,7 +6877,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN47" s="18" t="n">
+      <c r="AN47" s="3" t="n">
         <v>46195.67704861111</v>
       </c>
       <c r="AO47" t="inlineStr">
@@ -6470,6 +6913,26 @@
       <c r="BH47" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI47" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ47" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK47" t="inlineStr">
+        <is>
+          <t>app_patching</t>
+        </is>
+      </c>
+      <c r="BL47" t="inlineStr">
+        <is>
+          <t>network_isolation</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6975,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N48" s="18" t="n">
+      <c r="N48" s="3" t="n">
         <v>46203.37415509259</v>
       </c>
       <c r="O48" t="inlineStr">
@@ -6535,7 +6998,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X48" s="18" t="n">
+      <c r="X48" s="3" t="n">
         <v>46197.69813657407</v>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6548,7 +7011,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN48" s="18" t="n">
+      <c r="AN48" s="3" t="n">
         <v>46197.73563657407</v>
       </c>
       <c r="AO48" t="inlineStr">
@@ -6584,6 +7047,26 @@
       <c r="BH48" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI48" t="inlineStr">
+        <is>
+          <t>sensitive_operational</t>
+        </is>
+      </c>
+      <c r="BJ48" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK48" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL48" t="inlineStr">
+        <is>
+          <t>account_disable</t>
         </is>
       </c>
     </row>
@@ -6626,7 +7109,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N49" s="18" t="n">
+      <c r="N49" s="3" t="n">
         <v>46214.92612268519</v>
       </c>
       <c r="O49" t="inlineStr">
@@ -6649,7 +7132,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X49" s="18" t="n">
+      <c r="X49" s="3" t="n">
         <v>46208.47047453704</v>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6662,7 +7145,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN49" s="18" t="n">
+      <c r="AN49" s="3" t="n">
         <v>46208.49478009259</v>
       </c>
       <c r="AO49" t="inlineStr">
@@ -6698,6 +7181,26 @@
       <c r="BH49" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI49" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ49" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK49" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL49" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -6740,7 +7243,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N50" s="18" t="n">
+      <c r="N50" s="3" t="n">
         <v>46215.01686342592</v>
       </c>
       <c r="O50" t="inlineStr">
@@ -6763,7 +7266,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X50" s="18" t="n">
+      <c r="X50" s="3" t="n">
         <v>46210.2378125</v>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6776,7 +7279,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN50" s="18" t="n">
+      <c r="AN50" s="3" t="n">
         <v>46210.27045138889</v>
       </c>
       <c r="AO50" t="inlineStr">
@@ -6812,6 +7315,26 @@
       <c r="BH50" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI50" t="inlineStr">
+        <is>
+          <t>sensitive_operational</t>
+        </is>
+      </c>
+      <c r="BJ50" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK50" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL50" t="inlineStr">
+        <is>
+          <t>account_disable</t>
         </is>
       </c>
     </row>
@@ -6854,7 +7377,7 @@
           <t>Internal remediation complete. Details referred to police via ReportCyber.</t>
         </is>
       </c>
-      <c r="N51" s="18" t="n">
+      <c r="N51" s="3" t="n">
         <v>46222.29693287037</v>
       </c>
       <c r="O51" t="inlineStr">
@@ -6877,7 +7400,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X51" s="18" t="n">
+      <c r="X51" s="3" t="n">
         <v>46217.53197916667</v>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6890,7 +7413,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN51" s="18" t="n">
+      <c r="AN51" s="3" t="n">
         <v>46217.54517361111</v>
       </c>
       <c r="AO51" t="inlineStr">
@@ -6926,6 +7449,26 @@
       <c r="BH51" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI51" t="inlineStr">
+        <is>
+          <t>sensitive_operational</t>
+        </is>
+      </c>
+      <c r="BJ51" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK51" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL51" t="inlineStr">
+        <is>
+          <t>account_disable</t>
         </is>
       </c>
     </row>
@@ -6968,7 +7511,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N52" s="18" t="n">
+      <c r="N52" s="3" t="n">
         <v>46229.20216435185</v>
       </c>
       <c r="O52" t="inlineStr">
@@ -6991,7 +7534,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X52" s="18" t="n">
+      <c r="X52" s="3" t="n">
         <v>46222.53506944444</v>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7009,7 +7552,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN52" s="18" t="n">
+      <c r="AN52" s="3" t="n">
         <v>46222.578125</v>
       </c>
       <c r="AO52" t="inlineStr">
@@ -7045,6 +7588,26 @@
       <c r="BH52" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI52" t="inlineStr">
+        <is>
+          <t>private_information</t>
+        </is>
+      </c>
+      <c r="BJ52" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK52" t="inlineStr">
+        <is>
+          <t>harden_apps</t>
+        </is>
+      </c>
+      <c r="BL52" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7650,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N53" s="18" t="n">
+      <c r="N53" s="3" t="n">
         <v>46229.70789351852</v>
       </c>
       <c r="O53" t="inlineStr">
@@ -7110,7 +7673,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X53" s="18" t="n">
+      <c r="X53" s="3" t="n">
         <v>46224.26789351852</v>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7123,7 +7686,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN53" s="18" t="n">
+      <c r="AN53" s="3" t="n">
         <v>46224.27831018518</v>
       </c>
       <c r="AO53" t="inlineStr">
@@ -7159,6 +7722,26 @@
       <c r="BH53" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI53" t="inlineStr">
+        <is>
+          <t>sensitive_operational</t>
+        </is>
+      </c>
+      <c r="BJ53" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK53" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL53" t="inlineStr">
+        <is>
+          <t>account_disable</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7784,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N54" s="18" t="n">
+      <c r="N54" s="3" t="n">
         <v>46237.23</v>
       </c>
       <c r="O54" t="inlineStr">
@@ -7224,7 +7807,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X54" s="18" t="n">
+      <c r="X54" s="3" t="n">
         <v>46231.25847222222</v>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7237,7 +7820,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN54" s="18" t="n">
+      <c r="AN54" s="3" t="n">
         <v>46231.31958333333</v>
       </c>
       <c r="AO54" t="inlineStr">
@@ -7273,6 +7856,26 @@
       <c r="BH54" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI54" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ54" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK54" t="inlineStr">
+        <is>
+          <t>app_patching</t>
+        </is>
+      </c>
+      <c r="BL54" t="inlineStr">
+        <is>
+          <t>network_isolation</t>
         </is>
       </c>
     </row>
@@ -7315,7 +7918,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N55" s="18" t="n">
+      <c r="N55" s="3" t="n">
         <v>46243.33526620371</v>
       </c>
       <c r="O55" t="inlineStr">
@@ -7338,7 +7941,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X55" s="18" t="n">
+      <c r="X55" s="3" t="n">
         <v>46237.91267361111</v>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7351,7 +7954,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN55" s="18" t="n">
+      <c r="AN55" s="3" t="n">
         <v>46237.92170138889</v>
       </c>
       <c r="AO55" t="inlineStr">
@@ -7387,6 +7990,26 @@
       <c r="BH55" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI55" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ55" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK55" t="inlineStr">
+        <is>
+          <t>configure_macros</t>
+        </is>
+      </c>
+      <c r="BL55" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -7429,7 +8052,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N56" s="18" t="n">
+      <c r="N56" s="3" t="n">
         <v>46242.86603009259</v>
       </c>
       <c r="O56" t="inlineStr">
@@ -7452,7 +8075,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X56" s="18" t="n">
+      <c r="X56" s="3" t="n">
         <v>46238.14922453704</v>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7465,7 +8088,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN56" s="18" t="n">
+      <c r="AN56" s="3" t="n">
         <v>46238.19019675926</v>
       </c>
       <c r="AO56" t="inlineStr">
@@ -7501,6 +8124,26 @@
       <c r="BH56" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI56" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ56" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK56" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL56" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -7543,7 +8186,7 @@
           <t>Vendor released a clean update and confirmed root cause. Agent redeployed after verification.</t>
         </is>
       </c>
-      <c r="N57" s="18" t="n">
+      <c r="N57" s="3" t="n">
         <v>46249.70841435185</v>
       </c>
       <c r="O57" t="inlineStr">
@@ -7566,7 +8209,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X57" s="18" t="n">
+      <c r="X57" s="3" t="n">
         <v>46240.47518518518</v>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7579,7 +8222,7 @@
           <t>I2 — Widespread degradation</t>
         </is>
       </c>
-      <c r="AN57" s="18" t="n">
+      <c r="AN57" s="3" t="n">
         <v>46240.48837962963</v>
       </c>
       <c r="AO57" t="inlineStr">
@@ -7618,6 +8261,26 @@
       <c r="BH57" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI57" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ57" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK57" t="inlineStr">
+        <is>
+          <t>undetermined</t>
+        </is>
+      </c>
+      <c r="BL57" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -7660,7 +8323,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N58" s="18" t="n">
+      <c r="N58" s="3" t="n">
         <v>46263.07028935185</v>
       </c>
       <c r="O58" t="inlineStr">
@@ -7683,7 +8346,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X58" s="18" t="n">
+      <c r="X58" s="3" t="n">
         <v>46250.5384837963</v>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7696,7 +8359,7 @@
           <t>I1 — Full outage</t>
         </is>
       </c>
-      <c r="AN58" s="18" t="n">
+      <c r="AN58" s="3" t="n">
         <v>46250.56903935185</v>
       </c>
       <c r="AO58" t="inlineStr">
@@ -7735,6 +8398,26 @@
       <c r="BH58" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI58" t="inlineStr">
+        <is>
+          <t>sensitive_operational</t>
+        </is>
+      </c>
+      <c r="BJ58" t="inlineStr">
+        <is>
+          <t>regulated_essential_services</t>
+        </is>
+      </c>
+      <c r="BK58" t="inlineStr">
+        <is>
+          <t>backups</t>
+        </is>
+      </c>
+      <c r="BL58" t="inlineStr">
+        <is>
+          <t>network_isolation</t>
         </is>
       </c>
     </row>
@@ -7777,7 +8460,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N59" s="18" t="n">
+      <c r="N59" s="3" t="n">
         <v>46272.7130787037</v>
       </c>
       <c r="O59" t="inlineStr">
@@ -7800,7 +8483,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X59" s="18" t="n">
+      <c r="X59" s="3" t="n">
         <v>46264.20271990741</v>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7813,7 +8496,7 @@
           <t>I2 — Widespread degradation</t>
         </is>
       </c>
-      <c r="AN59" s="18" t="n">
+      <c r="AN59" s="3" t="n">
         <v>46264.23883101852</v>
       </c>
       <c r="AO59" t="inlineStr">
@@ -7849,6 +8532,26 @@
       <c r="BH59" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI59" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ59" t="inlineStr">
+        <is>
+          <t>regulated_essential_services</t>
+        </is>
+      </c>
+      <c r="BK59" t="inlineStr">
+        <is>
+          <t>undetermined</t>
+        </is>
+      </c>
+      <c r="BL59" t="inlineStr">
+        <is>
+          <t>firewall_rule</t>
         </is>
       </c>
     </row>
@@ -7891,7 +8594,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N60" s="18" t="n">
+      <c r="N60" s="3" t="n">
         <v>46272.31614583333</v>
       </c>
       <c r="O60" t="inlineStr">
@@ -7914,7 +8617,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X60" s="18" t="n">
+      <c r="X60" s="3" t="n">
         <v>46267.71045138889</v>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7927,7 +8630,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN60" s="18" t="n">
+      <c r="AN60" s="3" t="n">
         <v>46267.73753472222</v>
       </c>
       <c r="AO60" t="inlineStr">
@@ -7963,6 +8666,26 @@
       <c r="BH60" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI60" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ60" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK60" t="inlineStr">
+        <is>
+          <t>app_control</t>
+        </is>
+      </c>
+      <c r="BL60" t="inlineStr">
+        <is>
+          <t>system_shutdown</t>
         </is>
       </c>
     </row>
@@ -8005,7 +8728,7 @@
           <t>Internal remediation complete. Details referred to police via ReportCyber.</t>
         </is>
       </c>
-      <c r="N61" s="18" t="n">
+      <c r="N61" s="3" t="n">
         <v>46280.00303240741</v>
       </c>
       <c r="O61" t="inlineStr">
@@ -8028,7 +8751,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X61" s="18" t="n">
+      <c r="X61" s="3" t="n">
         <v>46275.33584490741</v>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8041,7 +8764,7 @@
           <t>I2 — Widespread degradation</t>
         </is>
       </c>
-      <c r="AN61" s="18" t="n">
+      <c r="AN61" s="3" t="n">
         <v>46275.35112268518</v>
       </c>
       <c r="AO61" t="inlineStr">
@@ -8077,6 +8800,26 @@
       <c r="BH61" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI61" t="inlineStr">
+        <is>
+          <t>sensitive_operational</t>
+        </is>
+      </c>
+      <c r="BJ61" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK61" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL61" t="inlineStr">
+        <is>
+          <t>account_disable</t>
         </is>
       </c>
     </row>
@@ -8119,7 +8862,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N62" s="18" t="n">
+      <c r="N62" s="3" t="n">
         <v>46287.33971064815</v>
       </c>
       <c r="O62" t="inlineStr">
@@ -8142,7 +8885,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X62" s="18" t="n">
+      <c r="X62" s="3" t="n">
         <v>46282.21601851852</v>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8155,7 +8898,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN62" s="18" t="n">
+      <c r="AN62" s="3" t="n">
         <v>46282.22574074074</v>
       </c>
       <c r="AO62" t="inlineStr">
@@ -8191,6 +8934,26 @@
       <c r="BH62" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI62" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ62" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK62" t="inlineStr">
+        <is>
+          <t>app_control</t>
+        </is>
+      </c>
+      <c r="BL62" t="inlineStr">
+        <is>
+          <t>system_shutdown</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8996,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N63" s="18" t="n">
+      <c r="N63" s="3" t="n">
         <v>46287.55907407407</v>
       </c>
       <c r="O63" t="inlineStr">
@@ -8256,7 +9019,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X63" s="18" t="n">
+      <c r="X63" s="3" t="n">
         <v>46282.89803240741</v>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8269,7 +9032,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN63" s="18" t="n">
+      <c r="AN63" s="3" t="n">
         <v>46282.95358796296</v>
       </c>
       <c r="AO63" t="inlineStr">
@@ -8305,6 +9068,26 @@
       <c r="BH63" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI63" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ63" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK63" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL63" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -8347,7 +9130,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N64" s="18" t="n">
+      <c r="N64" s="3" t="n">
         <v>46296.68609953704</v>
       </c>
       <c r="O64" t="inlineStr">
@@ -8370,7 +9153,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X64" s="18" t="n">
+      <c r="X64" s="3" t="n">
         <v>46291.51925925926</v>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8383,7 +9166,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN64" s="18" t="n">
+      <c r="AN64" s="3" t="n">
         <v>46291.57620370371</v>
       </c>
       <c r="AO64" t="inlineStr">
@@ -8419,6 +9202,26 @@
       <c r="BH64" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI64" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ64" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK64" t="inlineStr">
+        <is>
+          <t>undetermined</t>
+        </is>
+      </c>
+      <c r="BL64" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -8461,7 +9264,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N65" s="18" t="n">
+      <c r="N65" s="3" t="n">
         <v>46296.28091435185</v>
       </c>
       <c r="O65" t="inlineStr">
@@ -8484,7 +9287,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X65" s="18" t="n">
+      <c r="X65" s="3" t="n">
         <v>46291.61494212963</v>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8497,7 +9300,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN65" s="18" t="n">
+      <c r="AN65" s="3" t="n">
         <v>46291.62396990741</v>
       </c>
       <c r="AO65" t="inlineStr">
@@ -8533,6 +9336,26 @@
       <c r="BH65" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI65" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ65" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK65" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL65" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -8575,7 +9398,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N66" s="18" t="n">
+      <c r="N66" s="3" t="n">
         <v>46304.81336805555</v>
       </c>
       <c r="O66" t="inlineStr">
@@ -8598,7 +9421,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X66" s="18" t="n">
+      <c r="X66" s="3" t="n">
         <v>46298.0275</v>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8611,7 +9434,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN66" s="18" t="n">
+      <c r="AN66" s="3" t="n">
         <v>46298.08375</v>
       </c>
       <c r="AO66" t="inlineStr">
@@ -8647,6 +9470,26 @@
       <c r="BH66" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI66" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ66" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK66" t="inlineStr">
+        <is>
+          <t>undetermined</t>
+        </is>
+      </c>
+      <c r="BL66" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -8689,7 +9532,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N67" s="18" t="n">
+      <c r="N67" s="3" t="n">
         <v>46308.90711805555</v>
       </c>
       <c r="O67" t="inlineStr">
@@ -8712,7 +9555,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X67" s="18" t="n">
+      <c r="X67" s="3" t="n">
         <v>46304.36481481481</v>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8725,7 +9568,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN67" s="18" t="n">
+      <c r="AN67" s="3" t="n">
         <v>46304.39814814815</v>
       </c>
       <c r="AO67" t="inlineStr">
@@ -8761,6 +9604,26 @@
       <c r="BH67" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI67" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ67" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK67" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL67" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -8803,7 +9666,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N68" s="18" t="n">
+      <c r="N68" s="3" t="n">
         <v>46313.02425925926</v>
       </c>
       <c r="O68" t="inlineStr">
@@ -8826,7 +9689,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X68" s="18" t="n">
+      <c r="X68" s="3" t="n">
         <v>46308.3203587963</v>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8839,7 +9702,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN68" s="18" t="n">
+      <c r="AN68" s="3" t="n">
         <v>46308.37938657407</v>
       </c>
       <c r="AO68" t="inlineStr">
@@ -8875,6 +9738,26 @@
       <c r="BH68" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI68" t="inlineStr">
+        <is>
+          <t>sensitive_operational</t>
+        </is>
+      </c>
+      <c r="BJ68" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK68" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL68" t="inlineStr">
+        <is>
+          <t>account_disable</t>
         </is>
       </c>
     </row>
@@ -8917,7 +9800,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N69" s="18" t="n">
+      <c r="N69" s="3" t="n">
         <v>46313.82329861111</v>
       </c>
       <c r="O69" t="inlineStr">
@@ -8940,7 +9823,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X69" s="18" t="n">
+      <c r="X69" s="3" t="n">
         <v>46309.65038194445</v>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8953,7 +9836,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN69" s="18" t="n">
+      <c r="AN69" s="3" t="n">
         <v>46309.7121875</v>
       </c>
       <c r="AO69" t="inlineStr">
@@ -8989,6 +9872,26 @@
       <c r="BH69" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI69" t="inlineStr">
+        <is>
+          <t>sensitive_operational</t>
+        </is>
+      </c>
+      <c r="BJ69" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK69" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL69" t="inlineStr">
+        <is>
+          <t>account_disable</t>
         </is>
       </c>
     </row>
@@ -9031,7 +9934,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N70" s="18" t="n">
+      <c r="N70" s="3" t="n">
         <v>46318.41200231481</v>
       </c>
       <c r="O70" t="inlineStr">
@@ -9054,7 +9957,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X70" s="18" t="n">
+      <c r="X70" s="3" t="n">
         <v>46313.425</v>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9067,7 +9970,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN70" s="18" t="n">
+      <c r="AN70" s="3" t="n">
         <v>46313.44722222222</v>
       </c>
       <c r="AO70" t="inlineStr">
@@ -9103,6 +10006,26 @@
       <c r="BH70" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI70" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ70" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK70" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL70" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -9145,7 +10068,7 @@
           <t>Threat contained and removed. Affected accounts and devices remediated and monitoring confirmed no further activity.</t>
         </is>
       </c>
-      <c r="N71" s="18" t="n">
+      <c r="N71" s="3" t="n">
         <v>46318.99458333333</v>
       </c>
       <c r="O71" t="inlineStr">
@@ -9168,7 +10091,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X71" s="18" t="n">
+      <c r="X71" s="3" t="n">
         <v>46314.40141203703</v>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9181,7 +10104,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN71" s="18" t="n">
+      <c r="AN71" s="3" t="n">
         <v>46314.4180787037</v>
       </c>
       <c r="AO71" t="inlineStr">
@@ -9217,6 +10140,26 @@
       <c r="BH71" t="inlineStr">
         <is>
           <t>Closed</t>
+        </is>
+      </c>
+      <c r="BI71" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ71" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK71" t="inlineStr">
+        <is>
+          <t>app_control</t>
+        </is>
+      </c>
+      <c r="BL71" t="inlineStr">
+        <is>
+          <t>system_shutdown</t>
         </is>
       </c>
     </row>
@@ -9274,7 +10217,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X72" s="18" t="n">
+      <c r="X72" s="3" t="n">
         <v>46315.61111111111</v>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9287,7 +10230,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN72" s="18" t="n">
+      <c r="AN72" s="3" t="n">
         <v>46315.65625</v>
       </c>
       <c r="AO72" t="inlineStr">
@@ -9323,6 +10266,26 @@
       <c r="BH72" t="inlineStr">
         <is>
           <t>Resolved</t>
+        </is>
+      </c>
+      <c r="BI72" t="inlineStr">
+        <is>
+          <t>sensitive_operational</t>
+        </is>
+      </c>
+      <c r="BJ72" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK72" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL72" t="inlineStr">
+        <is>
+          <t>account_disable</t>
         </is>
       </c>
     </row>
@@ -9380,7 +10343,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X73" s="18" t="n">
+      <c r="X73" s="3" t="n">
         <v>46317.33680555555</v>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9393,7 +10356,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN73" s="18" t="n">
+      <c r="AN73" s="3" t="n">
         <v>46317.39722222222</v>
       </c>
       <c r="AO73" t="inlineStr">
@@ -9429,6 +10392,26 @@
       <c r="BH73" t="inlineStr">
         <is>
           <t>Resolved</t>
+        </is>
+      </c>
+      <c r="BI73" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ73" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK73" t="inlineStr">
+        <is>
+          <t>app_control</t>
+        </is>
+      </c>
+      <c r="BL73" t="inlineStr">
+        <is>
+          <t>system_shutdown</t>
         </is>
       </c>
     </row>
@@ -9486,7 +10469,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X74" s="18" t="n">
+      <c r="X74" s="3" t="n">
         <v>46317.8091087963</v>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9499,7 +10482,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN74" s="18" t="n">
+      <c r="AN74" s="3" t="n">
         <v>46317.85216435185</v>
       </c>
       <c r="AO74" t="inlineStr">
@@ -9535,6 +10518,26 @@
       <c r="BH74" t="inlineStr">
         <is>
           <t>Resolved</t>
+        </is>
+      </c>
+      <c r="BI74" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ74" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK74" t="inlineStr">
+        <is>
+          <t>undetermined</t>
+        </is>
+      </c>
+      <c r="BL74" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -9582,7 +10585,7 @@
           <t>Affected systems isolated and credentials reset.</t>
         </is>
       </c>
-      <c r="X75" s="18" t="n">
+      <c r="X75" s="3" t="n">
         <v>46318.6875</v>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9595,7 +10598,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN75" s="18" t="n">
+      <c r="AN75" s="3" t="n">
         <v>46318.70277777778</v>
       </c>
       <c r="AO75" t="inlineStr">
@@ -9631,6 +10634,26 @@
       <c r="BH75" t="inlineStr">
         <is>
           <t>Eradication</t>
+        </is>
+      </c>
+      <c r="BI75" t="inlineStr">
+        <is>
+          <t>sensitive_operational</t>
+        </is>
+      </c>
+      <c r="BJ75" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK75" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL75" t="inlineStr">
+        <is>
+          <t>account_disable</t>
         </is>
       </c>
     </row>
@@ -9688,7 +10711,7 @@
           <t>Malicious messages purged from mailboxes and sender blocked.</t>
         </is>
       </c>
-      <c r="X76" s="18" t="n">
+      <c r="X76" s="3" t="n">
         <v>46319.46875</v>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9701,7 +10724,7 @@
           <t>I4 — No impact/informational</t>
         </is>
       </c>
-      <c r="AN76" s="18" t="n">
+      <c r="AN76" s="3" t="n">
         <v>46319.49305555555</v>
       </c>
       <c r="AO76" t="inlineStr">
@@ -9737,6 +10760,26 @@
       <c r="BH76" t="inlineStr">
         <is>
           <t>Resolved</t>
+        </is>
+      </c>
+      <c r="BI76" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BJ76" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="BK76" t="inlineStr">
+        <is>
+          <t>mfa</t>
+        </is>
+      </c>
+      <c r="BL76" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -9779,7 +10822,7 @@
           <t>Self-service</t>
         </is>
       </c>
-      <c r="X77" s="18" t="n">
+      <c r="X77" s="3" t="n">
         <v>46320.26388888889</v>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9792,7 +10835,7 @@
           <t>I3 — Error, not preventing delivery of service</t>
         </is>
       </c>
-      <c r="AN77" s="18" t="n">
+      <c r="AN77" s="3" t="n">
         <v>46320.31805555556</v>
       </c>
       <c r="AO77" t="inlineStr">
@@ -9875,7 +10918,7 @@
           <t>Vendor remote access suspended. Affected servers isolated and privileged credentials rotated. Out-of-band communication channel in use.</t>
         </is>
       </c>
-      <c r="X78" s="18" t="n">
+      <c r="X78" s="3" t="n">
         <v>46316.32291666666</v>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9888,7 +10931,7 @@
           <t>I2 — Widespread degradation</t>
         </is>
       </c>
-      <c r="AN78" s="18" t="n">
+      <c r="AN78" s="3" t="n">
         <v>46316.34027777778</v>
       </c>
       <c r="AO78" t="inlineStr">
@@ -9929,589 +10972,28 @@
           <t>Containment</t>
         </is>
       </c>
+      <c r="BI78" t="inlineStr">
+        <is>
+          <t>critical_infrastructure,sensitive_operational</t>
+        </is>
+      </c>
+      <c r="BJ78" t="inlineStr">
+        <is>
+          <t>regulated_essential_services</t>
+        </is>
+      </c>
+      <c r="BK78" t="inlineStr">
+        <is>
+          <t>restrict_admin</t>
+        </is>
+      </c>
+      <c r="BL78" t="inlineStr">
+        <is>
+          <t>third_party_engagement</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="32">
-    <dataValidation sqref="A2:A32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" errorStyle="stop" operator="between">
-      <formula1>18264.000694444443</formula1>
-      <formula2>54789.00069444445</formula2>
-    </dataValidation>
-    <dataValidation sqref="B2:B32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
-      <formula1>choice_values1</formula1>
-    </dataValidation>
-    <dataValidation sqref="C2:C32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D2:D32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
-      <formula1>choice_values3</formula1>
-    </dataValidation>
-    <dataValidation sqref="E2:E32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" errorStyle="stop" operator="between">
-      <formula1>18264.000694444443</formula1>
-      <formula2>54789.00069444445</formula2>
-    </dataValidation>
-    <dataValidation sqref="H2:H32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
-      <formula1>choice_values7</formula1>
-    </dataValidation>
-    <dataValidation sqref="L2:L32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
-      <formula1>choice_values11</formula1>
-    </dataValidation>
-    <dataValidation sqref="N2:N32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" errorStyle="stop" operator="between">
-      <formula1>18264.000694444443</formula1>
-      <formula2>54789.00069444445</formula2>
-    </dataValidation>
-    <dataValidation sqref="S2:S32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
-      <formula1>choice_values18</formula1>
-    </dataValidation>
-    <dataValidation sqref="X2:X32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" errorStyle="stop" operator="between">
-      <formula1>18264.000694444443</formula1>
-      <formula2>54789.00069444445</formula2>
-    </dataValidation>
-    <dataValidation sqref="AB2:AB32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" errorStyle="stop" operator="between">
-      <formula1>18264.000694444443</formula1>
-      <formula2>54789.00069444445</formula2>
-    </dataValidation>
-    <dataValidation sqref="AC2:AC32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
-      <formula1>choice_values28</formula1>
-    </dataValidation>
-    <dataValidation sqref="AD2:AD32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" errorStyle="stop" operator="between">
-      <formula1>18264.000694444443</formula1>
-      <formula2>54789.00069444445</formula2>
-    </dataValidation>
-    <dataValidation sqref="AE2:AE32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" errorStyle="stop" operator="between">
-      <formula1>18264.000694444443</formula1>
-      <formula2>54789.00069444445</formula2>
-    </dataValidation>
-    <dataValidation sqref="AF2:AF32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
-      <formula1>choice_values31</formula1>
-    </dataValidation>
-    <dataValidation sqref="AG2:AG32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AI2:AI32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AK2:AK32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AM2:AM32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
-      <formula1>choice_values38</formula1>
-    </dataValidation>
-    <dataValidation sqref="AN2:AN32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" errorStyle="stop" operator="between">
-      <formula1>18264.000694444443</formula1>
-      <formula2>54789.00069444445</formula2>
-    </dataValidation>
-    <dataValidation sqref="AR2:AR32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" errorStyle="stop" operator="between">
-      <formula1>18264.000694444443</formula1>
-      <formula2>54789.00069444445</formula2>
-    </dataValidation>
-    <dataValidation sqref="AS2:AS32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AT2:AT32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
-      <formula1>choice_values45</formula1>
-    </dataValidation>
-    <dataValidation sqref="AU2:AU32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AV2:AV32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="AZ2:AZ32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
-      <formula1>choice_values51</formula1>
-    </dataValidation>
-    <dataValidation sqref="BA2:BA32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
-      <formula1>choice_values52</formula1>
-    </dataValidation>
-    <dataValidation sqref="BC2:BC32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
-      <formula1>choice_values54</formula1>
-    </dataValidation>
-    <dataValidation sqref="BD2:BD32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
-      <formula1>choice_values55</formula1>
-    </dataValidation>
-    <dataValidation sqref="BE2:BE32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
-      <formula1>choice_values56</formula1>
-    </dataValidation>
-    <dataValidation sqref="BF2:BF32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" errorStyle="stop" operator="between">
-      <formula1>18264.000694444443</formula1>
-      <formula2>54789.00069444445</formula2>
-    </dataValidation>
-    <dataValidation sqref="BG2:BG32001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" errorStyle="stop" operator="between">
-      <formula1>18264.000694444443</formula1>
-      <formula2>54789.00069444445</formula2>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B1:BE19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>-- None --</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Not Yet Requested</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>-- None --</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>-- None --</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>-- None --</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Pending Assessment</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>I1 — Full outage</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>-- None --</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>-- None --</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>-- None --</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>-- None --</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>-- None --</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>-- None --</t>
-        </is>
-      </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>1 - High</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>C1 - Sustained Disruption</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Requested</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Botnet</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Threat neutralised</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Eligible</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>I2 — Widespread degradation</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Awaiting forensics</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>1 - Critical</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>Nation-state</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>Malware</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>Proceed to Next Task</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>Cancel all future Tasks</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>2 - Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>C2 - Extensive Compromise</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Not determined</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>False positive</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Not Eligible – Remediated</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>I3 — Error, not preventing delivery of service</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Awaiting law enforcement</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>2 - High</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>Cybercriminal</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>Phishing</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>Wait for a User to Close this task</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>Go to a previous Task</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>3 - Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>C3 - Isolated/Coordinated Compromise</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Compromised software updates</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Handed to law enforcement</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Self-service</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Not Eligible - Low Risk</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>I4 — No impact/informational</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Awaiting vendor</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>3 - Moderate</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>Hacktivist</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>Ransomware</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>C4 - Low-Level Attack</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Credential stuffing</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Resolved by vendor</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Virtual Agent</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Awaiting ASD response</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>4 - Low</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>Insider</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>Data breach</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>C6 - Unsuccessful Attack</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Email spoofing</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Unresolved</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Walk-in</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>Denial of service</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Malicious email attachment</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>Business email compromise</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Application layer flooding</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>Supply chain compromise</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Brute force attack</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>Unauthorised access</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Drive by download</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>Not determined</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Look alike domain</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Trusted vendor pivot</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Infected removable media</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Malicious open source dependency</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Smishing</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Vulnerability exploit</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Deepfake</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Security misconfiguration</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Session hijacking</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>